--- a/artfynd/A 17972-2024 artfynd.xlsx
+++ b/artfynd/A 17972-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>4565943</v>
       </c>
       <c r="B2" t="n">
-        <v>96943</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99771</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602488.9992517657</v>
+        <v>602489</v>
       </c>
       <c r="R2" t="n">
-        <v>6672389.079946622</v>
+        <v>6672389</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -751,19 +746,9 @@
           <t>1993-08-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1993-08-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -808,7 +793,7 @@
         <v>70121786</v>
       </c>
       <c r="B3" t="n">
-        <v>99707</v>
+        <v>99848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,6 +894,117 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>70121531</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99898</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222332</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Repestarr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carex loliacea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>250 m VNV om Nystrand, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>602493</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6672494</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1993-01-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1993-12-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>skogskärr</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lennart Karlén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Upplands Flora 2010</t>
         </is>

--- a/artfynd/A 17972-2024 artfynd.xlsx
+++ b/artfynd/A 17972-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4565943</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70121786</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,8 +1024,18 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70121531</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>